--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegist001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegist001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="15210" windowHeight="3480"/>
+    <workbookView xWindow="0" yWindow="2712" windowWidth="15216" windowHeight="3480"/>
   </bookViews>
   <sheets>
     <sheet name="投资者持有信息登记" sheetId="1" r:id="rId1"/>
@@ -22,12 +27,11 @@
     <definedName name="银行">#REF!</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
   </si>
@@ -686,6 +690,10 @@
     <t>**折算人民币金额（元）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -694,7 +702,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,7 +904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -924,10 +932,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1239,15 +1243,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="21" style="6" customWidth="1"/>
-    <col min="7" max="7" width="22.125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" style="7" customWidth="1"/>
     <col min="8" max="8" width="28" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="8.875" style="8"/>
+    <col min="9" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" customHeight="1">
+    <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>188</v>
       </c>
@@ -1273,15 +1277,10 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>196</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1305,926 +1304,926 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A184"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="82.625" customWidth="1"/>
+    <col min="1" max="1" width="82.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="48" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="37.5" customHeight="1">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
-      <c r="A3" s="20" t="s">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.25">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="18" customFormat="1" ht="14.25">
-      <c r="A5" s="20"/>
-    </row>
-    <row r="6" spans="1:1" ht="14.25">
-      <c r="A6" s="12" t="s">
+    <row r="5" spans="1:1" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+    </row>
+    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.9">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="13.9">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="13.9">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="13.9">
-      <c r="A26" s="13" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="13.9">
-      <c r="A27" s="13" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="13.9">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="13.9">
-      <c r="A29" s="13" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="13.9">
-      <c r="A30" s="13" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="13.9">
-      <c r="A31" s="13" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="13.9">
-      <c r="A32" s="13" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="13.9">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="13.9">
-      <c r="A34" s="14" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="13.9">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="13.9">
-      <c r="A36" s="14" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="13.9">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="13.9">
-      <c r="A38" s="14" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="13.9">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="13.9">
-      <c r="A40" s="14" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="13.9">
-      <c r="A41" s="14" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="13.9">
-      <c r="A42" s="14" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="13.9">
-      <c r="A43" s="14" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="13.9">
-      <c r="A44" s="14" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="13.9">
-      <c r="A45" s="14" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="13.9">
-      <c r="A46" s="14" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="13.9">
-      <c r="A47" s="14" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="13.9">
-      <c r="A48" s="14" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="13.9">
-      <c r="A49" s="14" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="13.9">
-      <c r="A50" s="14" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="13.9">
-      <c r="A51" s="14" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="13.9">
-      <c r="A52" s="14" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="13.9">
-      <c r="A53" s="14" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="13.9">
-      <c r="A54" s="14" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="13.9">
-      <c r="A55" s="14" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="13.9">
-      <c r="A56" s="14" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="13.9">
-      <c r="A57" s="14" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="13.9">
-      <c r="A58" s="14" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="13.9">
-      <c r="A59" s="14" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="13.9">
-      <c r="A60" s="14" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="13.9">
-      <c r="A61" s="14" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="13.9">
-      <c r="A62" s="14" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="13.9">
-      <c r="A63" s="14" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="13.9">
-      <c r="A64" s="14" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="13.9">
-      <c r="A65" s="14" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="13.9">
-      <c r="A66" s="14" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="13.9">
-      <c r="A67" s="14" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="13.9">
-      <c r="A68" s="14" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="13.9">
-      <c r="A69" s="14" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="13.9">
-      <c r="A70" s="14" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="13.9">
-      <c r="A71" s="14" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="13.9">
-      <c r="A72" s="14" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="13.9">
-      <c r="A73" s="14" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="13.9">
-      <c r="A74" s="14" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="13.9">
-      <c r="A75" s="14" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="13.9">
-      <c r="A76" s="14" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="13.9">
-      <c r="A77" s="14" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="13.9">
-      <c r="A78" s="14" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="13.9">
-      <c r="A79" s="14" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="13.9">
-      <c r="A80" s="14" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="13.9">
-      <c r="A81" s="14" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="13.9">
-      <c r="A82" s="14" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="13.9">
-      <c r="A83" s="14" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="13.9">
-      <c r="A84" s="14" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="13.9">
-      <c r="A85" s="14" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="13.9">
-      <c r="A86" s="14" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="13.9">
-      <c r="A87" s="14" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="13.9">
-      <c r="A88" s="14" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="13.9">
-      <c r="A89" s="14" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="13.9">
-      <c r="A90" s="14" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="13.9">
-      <c r="A91" s="14" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="13.9">
-      <c r="A92" s="14" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="13.9">
-      <c r="A93" s="14" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="13" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="13.9">
-      <c r="A94" s="14" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="13.9">
-      <c r="A95" s="14" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="13.9">
-      <c r="A96" s="14" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" ht="13.9">
-      <c r="A97" s="14" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="13.9">
-      <c r="A98" s="14" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="13.9">
-      <c r="A99" s="14" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="13.9">
-      <c r="A100" s="14" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" ht="13.9">
-      <c r="A101" s="14" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="13.9">
-      <c r="A102" s="14" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" ht="13.9">
-      <c r="A103" s="14" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="13.9">
-      <c r="A104" s="14" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="13.9">
-      <c r="A105" s="14" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="13.9">
-      <c r="A106" s="14" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="13.9">
-      <c r="A107" s="14" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="13.9">
-      <c r="A108" s="14" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" ht="13.9">
-      <c r="A109" s="14" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="13.9">
-      <c r="A110" s="14" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="13" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" ht="13.9">
-      <c r="A111" s="14" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="13" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="13.9">
-      <c r="A112" s="14" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="13.9">
-      <c r="A113" s="14" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="13.9">
-      <c r="A114" s="14" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="13.9">
-      <c r="A115" s="14" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="13.9">
-      <c r="A116" s="14" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="13" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" ht="13.9">
-      <c r="A117" s="14" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" ht="13.9">
-      <c r="A118" s="14" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" ht="13.9">
-      <c r="A119" s="14" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="13" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" ht="13.9">
-      <c r="A120" s="14" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" ht="13.9">
-      <c r="A121" s="14" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" ht="13.9">
-      <c r="A122" s="14" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="13" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" ht="13.9">
-      <c r="A123" s="14" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" ht="13.9">
-      <c r="A124" s="14" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" ht="13.9">
-      <c r="A125" s="14" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" ht="13.9">
-      <c r="A126" s="14" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" ht="13.9">
-      <c r="A127" s="14" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" ht="13.9">
-      <c r="A128" s="14" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="13" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="13.9">
-      <c r="A129" s="14" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="13" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="13.9">
-      <c r="A130" s="14" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" ht="13.9">
-      <c r="A131" s="14" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="13" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="13.9">
-      <c r="A132" s="14" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="13" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="13.9">
-      <c r="A133" s="14" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="13" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="13.9">
-      <c r="A134" s="14" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" ht="13.9">
-      <c r="A135" s="14" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="13" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="13.9">
-      <c r="A136" s="14" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="13" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" ht="13.9">
-      <c r="A137" s="14" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" ht="13.9">
-      <c r="A138" s="14" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="13" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="13.9">
-      <c r="A139" s="14" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" ht="13.9">
-      <c r="A140" s="14" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="13" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" ht="13.9">
-      <c r="A141" s="14" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" ht="13.9">
-      <c r="A142" s="14" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="13" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" ht="13.9">
-      <c r="A143" s="14" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="13" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" ht="13.9">
-      <c r="A144" s="14" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="13" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="13.9">
-      <c r="A145" s="14" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="13" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" ht="13.9">
-      <c r="A146" s="14" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="13" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" ht="13.9">
-      <c r="A147" s="14" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" ht="13.9">
-      <c r="A148" s="14" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="13" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" ht="13.9">
-      <c r="A149" s="14" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" ht="13.9">
-      <c r="A150" s="14" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" ht="13.9">
-      <c r="A151" s="14" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" ht="13.9">
-      <c r="A152" s="14" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="13" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" ht="13.9">
-      <c r="A153" s="14" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="13" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" ht="13.9">
-      <c r="A154" s="14" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" ht="13.9">
-      <c r="A155" s="14" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="13" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" ht="13.9">
-      <c r="A156" s="14" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" ht="13.9">
-      <c r="A157" s="14" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="13" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" ht="13.9">
-      <c r="A158" s="14" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="13" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" ht="13.9">
-      <c r="A159" s="14" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="13" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" ht="13.9">
-      <c r="A160" s="14" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="13" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" ht="13.9">
-      <c r="A161" s="14" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="13" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" ht="13.9">
-      <c r="A162" s="14" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="13" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" ht="13.9">
-      <c r="A163" s="14" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="13" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" ht="13.9">
-      <c r="A164" s="14" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="13" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" ht="13.9">
-      <c r="A165" s="14" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="13" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" ht="13.9">
-      <c r="A166" s="14" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="13" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" ht="13.9">
-      <c r="A167" s="14" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="13" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" ht="13.9">
-      <c r="A168" s="14" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="13" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" ht="13.9">
-      <c r="A169" s="14" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" ht="13.9">
-      <c r="A170" s="14" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="13" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" ht="13.9">
-      <c r="A171" s="14" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="13" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" ht="13.9">
-      <c r="A172" s="14" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="13" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" ht="13.9">
-      <c r="A173" s="14" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="13" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" ht="13.9">
-      <c r="A174" s="14" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="13" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" ht="13.9">
-      <c r="A175" s="14" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="13" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" ht="13.9">
-      <c r="A176" s="14" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="13" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" ht="13.9">
-      <c r="A177" s="14" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" ht="13.9">
-      <c r="A178" s="14" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="13" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:1" ht="13.9">
-      <c r="A179" s="14" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="13" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:1" ht="13.9">
-      <c r="A180" s="14" t="s">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="13" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:1" ht="13.9">
-      <c r="A181" s="14" t="s">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="13" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:1" ht="13.9">
-      <c r="A182" s="14" t="s">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="13" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:1" ht="13.9">
-      <c r="A183" s="14" t="s">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="13" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" ht="13.9">
-      <c r="A184" s="15" t="s">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="14" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2238,12 +2237,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.875" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2251,7 +2250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -2259,11 +2258,11 @@
         <v>43250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="67.5">
+    <row r="3" spans="1:2" ht="69" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegist001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorsHoldInfoRegist001.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
   </si>
@@ -688,10 +688,6 @@
   </si>
   <si>
     <t>**折算人民币金额（元）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -904,7 +900,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -920,11 +916,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -958,6 +949,13 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1245,42 +1243,47 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="21" style="6" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="28" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="6" width="21" style="18" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" style="19" customWidth="1"/>
+    <col min="8" max="8" width="28" style="18" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>196</v>
-      </c>
+    <row r="2" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1310,920 +1313,920 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
+    <row r="5" spans="1:1" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
     </row>
     <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="11" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="11" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="11" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="11" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="11" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="11" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="11" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="11" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="11" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="11" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="11" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="11" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="11" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="11" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="11" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="11" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="11" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="11" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="13" t="s">
+      <c r="A111" s="11" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="11" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="11" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="11" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="13" t="s">
+      <c r="A121" s="11" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="11" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="11" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="11" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="11" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="11" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="11" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="13" t="s">
+      <c r="A133" s="11" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="11" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="13" t="s">
+      <c r="A135" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="13" t="s">
+      <c r="A138" s="11" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="11" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="11" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="13" t="s">
+      <c r="A141" s="11" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="13" t="s">
+      <c r="A142" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="13" t="s">
+      <c r="A143" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="11" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="13" t="s">
+      <c r="A146" s="11" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="13" t="s">
+      <c r="A147" s="11" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="13" t="s">
+      <c r="A148" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="13" t="s">
+      <c r="A149" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="13" t="s">
+      <c r="A150" s="11" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="13" t="s">
+      <c r="A151" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="13" t="s">
+      <c r="A152" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="13" t="s">
+      <c r="A153" s="11" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="13" t="s">
+      <c r="A154" s="11" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="13" t="s">
+      <c r="A155" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="13" t="s">
+      <c r="A156" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="13" t="s">
+      <c r="A157" s="11" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="13" t="s">
+      <c r="A158" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="13" t="s">
+      <c r="A159" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="13" t="s">
+      <c r="A160" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="13" t="s">
+      <c r="A161" s="11" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="13" t="s">
+      <c r="A162" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="13" t="s">
+      <c r="A163" s="11" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="13" t="s">
+      <c r="A164" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="13" t="s">
+      <c r="A165" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="13" t="s">
+      <c r="A166" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="13" t="s">
+      <c r="A167" s="11" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="13" t="s">
+      <c r="A168" s="11" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="13" t="s">
+      <c r="A169" s="11" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="13" t="s">
+      <c r="A170" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="13" t="s">
+      <c r="A171" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="13" t="s">
+      <c r="A172" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="13" t="s">
+      <c r="A173" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="13" t="s">
+      <c r="A174" s="11" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="13" t="s">
+      <c r="A175" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="13" t="s">
+      <c r="A176" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="13" t="s">
+      <c r="A177" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="13" t="s">
+      <c r="A178" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="13" t="s">
+      <c r="A179" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="13" t="s">
+      <c r="A180" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="13" t="s">
+      <c r="A181" s="11" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="13" t="s">
+      <c r="A182" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="13" t="s">
+      <c r="A183" s="11" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="14" t="s">
+      <c r="A184" s="12" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2262,7 +2265,7 @@
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>185</v>
       </c>
     </row>
